--- a/01_data/01_input_data/02_processed/data_base_case_russia.xlsx
+++ b/01_data/01_input_data/02_processed/data_base_case_russia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A4A7F1-907B-4807-ACA6-A4F206FD9687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3785F8-1B7B-45C1-A856-923DC1D3743A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="97">
   <si>
     <t>Commodities</t>
   </si>
@@ -271,9 +271,6 @@
   </si>
   <si>
     <t>AZ</t>
-  </si>
-  <si>
-    <t>TK</t>
   </si>
   <si>
     <t>MA</t>
@@ -761,7 +758,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
@@ -971,7 +968,7 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
@@ -1001,92 +998,92 @@
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
@@ -1146,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B152"/>
+  <dimension ref="A1:B150"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1255,10 +1252,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1983,7 +1980,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B105" t="s">
         <v>34</v>
@@ -2034,7 +2031,7 @@
         <v>76</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -2103,15 +2100,15 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="B120" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B121" t="s">
         <v>34</v>
@@ -2119,10 +2116,10 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B122" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -2130,7 +2127,7 @@
         <v>48</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -2138,7 +2135,7 @@
         <v>48</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -2146,7 +2143,7 @@
         <v>48</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -2154,15 +2151,15 @@
         <v>48</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -2170,28 +2167,28 @@
         <v>38</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
+        <v>20</v>
+      </c>
+      <c r="B130" t="s">
         <v>74</v>
-      </c>
-      <c r="B130" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B131" t="s">
         <v>74</v>
@@ -2199,169 +2196,153 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B132" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B133" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B134" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B135" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B136" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B137" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B139" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B140" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B141" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B142" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B143" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B144" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B145" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B146" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B148" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B149" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B150" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>40</v>
-      </c>
-      <c r="B151" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>53</v>
-      </c>
-      <c r="B152" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2372,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I302"/>
+  <dimension ref="A1:I300"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2757,7 +2738,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
         <v>74</v>
@@ -2786,10 +2767,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
         <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
       </c>
       <c r="D15">
         <v>10000</v>
@@ -2815,7 +2796,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
         <v>60</v>
@@ -2844,7 +2825,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -2873,7 +2854,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
         <v>68</v>
@@ -2902,7 +2883,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
@@ -2931,7 +2912,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
@@ -2960,7 +2941,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -2989,7 +2970,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
         <v>20</v>
@@ -3018,7 +2999,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -3047,7 +3028,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
         <v>59</v>
@@ -3076,7 +3057,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
         <v>67</v>
@@ -3105,7 +3086,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
@@ -3134,7 +3115,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
         <v>64</v>
@@ -3163,7 +3144,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
@@ -3192,7 +3173,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
@@ -3221,10 +3202,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -5831,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C120" t="s">
         <v>34</v>
@@ -5860,16 +5841,16 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C121" t="s">
         <v>22</v>
       </c>
       <c r="D121">
-        <v>415.40649999999994</v>
+        <v>173.667</v>
       </c>
       <c r="E121">
-        <v>415.40649999999994</v>
+        <v>173.667</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5889,16 +5870,16 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C122" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D122">
-        <v>173.667</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E122">
-        <v>173.667</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5918,10 +5899,10 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
+        <v>53</v>
+      </c>
+      <c r="C123" t="s">
         <v>75</v>
-      </c>
-      <c r="C123" t="s">
-        <v>30</v>
       </c>
       <c r="D123">
         <v>439.27749999999992</v>
@@ -5947,16 +5928,16 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C124" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D124">
-        <v>439.27749999999992</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="E124">
-        <v>439.27749999999992</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5976,16 +5957,16 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C125" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D125">
-        <v>118.77099999999999</v>
+        <v>486.91</v>
       </c>
       <c r="E125">
-        <v>118.77099999999999</v>
+        <v>486.91</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -6005,16 +5986,16 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C126" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D126">
-        <v>486.91</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E126">
-        <v>486.91</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -6034,16 +6015,16 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C127" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D127">
-        <v>144.17500000000001</v>
+        <v>49.494</v>
       </c>
       <c r="E127">
-        <v>144.17500000000001</v>
+        <v>49.494</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -6066,13 +6047,13 @@
         <v>58</v>
       </c>
       <c r="C128" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D128">
-        <v>49.494</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="E128">
-        <v>49.494</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -6095,13 +6076,13 @@
         <v>58</v>
       </c>
       <c r="C129" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D129">
-        <v>816.06700000000012</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="E129">
-        <v>816.06700000000012</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -6121,16 +6102,16 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C130" t="s">
         <v>66</v>
       </c>
       <c r="D130">
-        <v>188.88749999999999</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="E130">
-        <v>188.88749999999999</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6150,16 +6131,16 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
+        <v>68</v>
+      </c>
+      <c r="C131" t="s">
         <v>67</v>
       </c>
-      <c r="C131" t="s">
-        <v>66</v>
-      </c>
       <c r="D131">
-        <v>89.716999999999999</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="E131">
-        <v>89.716999999999999</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6182,13 +6163,13 @@
         <v>68</v>
       </c>
       <c r="C132" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D132">
-        <v>170.63749999999999</v>
+        <v>12.1837</v>
       </c>
       <c r="E132">
-        <v>170.63749999999999</v>
+        <v>12.1837</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6208,16 +6189,16 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
+        <v>36</v>
+      </c>
+      <c r="C133" t="s">
         <v>68</v>
       </c>
-      <c r="C133" t="s">
-        <v>70</v>
-      </c>
       <c r="D133">
-        <v>12.1837</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="E133">
-        <v>12.1837</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -6237,16 +6218,16 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C134" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D134">
-        <v>256.15699999999998</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="E134">
-        <v>256.15699999999998</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -6266,16 +6247,16 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C135" t="s">
         <v>22</v>
       </c>
       <c r="D135">
-        <v>180.20050000000001</v>
+        <v>421.21</v>
       </c>
       <c r="E135">
-        <v>180.20050000000001</v>
+        <v>421.21</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -6295,16 +6276,16 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C136" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D136">
-        <v>421.21</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E136">
-        <v>421.21</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6324,16 +6305,16 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C137" t="s">
         <v>34</v>
       </c>
       <c r="D137">
-        <v>123.04150000000001</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="E137">
-        <v>123.04150000000001</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6353,16 +6334,16 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C138" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D138">
-        <v>161.62200000000001</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="E138">
-        <v>161.62200000000001</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6385,13 +6366,13 @@
         <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D139">
-        <v>455.15499999999997</v>
+        <v>351.714</v>
       </c>
       <c r="E139">
-        <v>455.15499999999997</v>
+        <v>351.714</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6414,13 +6395,13 @@
         <v>48</v>
       </c>
       <c r="C140" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D140">
-        <v>351.714</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="E140">
-        <v>351.714</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -6443,13 +6424,13 @@
         <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D141">
-        <v>167.75399999999999</v>
+        <v>207.5025</v>
       </c>
       <c r="E141">
-        <v>167.75399999999999</v>
+        <v>207.5025</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -6472,13 +6453,13 @@
         <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D142">
-        <v>207.5025</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="E142">
-        <v>207.5025</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -6498,16 +6479,16 @@
         <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C143" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D143">
-        <v>513.19000000000005</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="E143">
-        <v>513.19000000000005</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -6530,13 +6511,13 @@
         <v>38</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D144">
-        <v>82.927999999999997</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="E144">
-        <v>82.927999999999997</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -6556,16 +6537,16 @@
         <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D145">
-        <v>67.451999999999998</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E145">
-        <v>67.451999999999998</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6585,10 +6566,10 @@
         <v>11</v>
       </c>
       <c r="B146" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" t="s">
         <v>74</v>
-      </c>
-      <c r="C146" t="s">
-        <v>22</v>
       </c>
       <c r="D146">
         <v>200.71350000000001</v>
@@ -6614,16 +6595,16 @@
         <v>11</v>
       </c>
       <c r="B147" t="s">
+        <v>36</v>
+      </c>
+      <c r="C147" t="s">
         <v>20</v>
       </c>
-      <c r="C147" t="s">
-        <v>74</v>
-      </c>
       <c r="D147">
-        <v>200.71350000000001</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E147">
-        <v>200.71350000000001</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -6643,16 +6624,16 @@
         <v>11</v>
       </c>
       <c r="B148" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" t="s">
         <v>77</v>
       </c>
-      <c r="C148" t="s">
-        <v>20</v>
-      </c>
       <c r="D148">
-        <v>144.17500000000001</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E148">
-        <v>144.17500000000001</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -6672,16 +6653,16 @@
         <v>11</v>
       </c>
       <c r="B149" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C149" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="D149">
-        <v>123.04150000000001</v>
+        <v>421.21</v>
       </c>
       <c r="E149">
-        <v>123.04150000000001</v>
+        <v>421.21</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -6701,16 +6682,16 @@
         <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C150" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="D150">
-        <v>421.21</v>
+        <v>14.965</v>
       </c>
       <c r="E150">
-        <v>421.21</v>
+        <v>14.965</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -6727,19 +6708,19 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D151">
-        <v>14.965</v>
+        <v>500</v>
       </c>
       <c r="E151">
-        <v>14.965</v>
+        <v>500</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -6748,7 +6729,7 @@
         <v>10000000</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -6759,10 +6740,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D152">
         <v>500</v>
@@ -6788,10 +6769,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C153" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D153">
         <v>500</v>
@@ -6817,10 +6798,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D154">
         <v>500</v>
@@ -6846,10 +6827,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C155" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D155">
         <v>500</v>
@@ -6875,10 +6856,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D156">
         <v>500</v>
@@ -6904,10 +6885,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C157" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D157">
         <v>500</v>
@@ -6933,10 +6914,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C158" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6962,10 +6943,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C159" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6991,10 +6972,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C160" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -7020,10 +7001,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C161" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -7049,10 +7030,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C162" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -7078,10 +7059,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C163" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -7107,10 +7088,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C164" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -7136,10 +7117,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C165" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -7165,10 +7146,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C166" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -7194,10 +7175,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C167" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -7223,10 +7204,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -7252,10 +7233,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C169" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7281,10 +7262,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C170" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7310,10 +7291,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C171" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7339,10 +7320,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C172" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7368,10 +7349,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C173" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7397,10 +7378,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C174" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7426,10 +7407,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C175" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7455,10 +7436,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C176" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7487,7 +7468,7 @@
         <v>38</v>
       </c>
       <c r="C177" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7513,10 +7494,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="s">
         <v>38</v>
-      </c>
-      <c r="C178" t="s">
-        <v>59</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7545,7 +7526,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7574,7 +7555,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7603,7 +7584,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7629,10 +7610,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
+        <v>28</v>
+      </c>
+      <c r="C182" t="s">
         <v>16</v>
-      </c>
-      <c r="C182" t="s">
-        <v>18</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7661,7 +7642,7 @@
         <v>28</v>
       </c>
       <c r="C183" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D183">
         <v>500</v>
@@ -7687,10 +7668,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C184" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7719,7 +7700,7 @@
         <v>42</v>
       </c>
       <c r="C185" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7748,7 +7729,7 @@
         <v>42</v>
       </c>
       <c r="C186" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7777,7 +7758,7 @@
         <v>42</v>
       </c>
       <c r="C187" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7806,7 +7787,7 @@
         <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7835,7 +7816,7 @@
         <v>42</v>
       </c>
       <c r="C189" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7864,7 +7845,7 @@
         <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7893,7 +7874,7 @@
         <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7922,7 +7903,7 @@
         <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7948,10 +7929,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
+        <v>60</v>
+      </c>
+      <c r="C193" t="s">
         <v>42</v>
-      </c>
-      <c r="C193" t="s">
-        <v>63</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7980,7 +7961,7 @@
         <v>60</v>
       </c>
       <c r="C194" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -8009,7 +7990,7 @@
         <v>60</v>
       </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -8038,7 +8019,7 @@
         <v>60</v>
       </c>
       <c r="C196" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -8067,7 +8048,7 @@
         <v>60</v>
       </c>
       <c r="C197" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -8093,10 +8074,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
+        <v>22</v>
+      </c>
+      <c r="C198" t="s">
         <v>60</v>
-      </c>
-      <c r="C198" t="s">
-        <v>66</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -8125,7 +8106,7 @@
         <v>22</v>
       </c>
       <c r="C199" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -8154,7 +8135,7 @@
         <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -8180,10 +8161,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="C201" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -8212,7 +8193,7 @@
         <v>61</v>
       </c>
       <c r="C202" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -8241,7 +8222,7 @@
         <v>61</v>
       </c>
       <c r="C203" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -8267,10 +8248,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C204" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8299,7 +8280,7 @@
         <v>64</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8325,10 +8306,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
+        <v>24</v>
+      </c>
+      <c r="C206" t="s">
         <v>64</v>
-      </c>
-      <c r="C206" t="s">
-        <v>24</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8357,7 +8338,7 @@
         <v>24</v>
       </c>
       <c r="C207" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D207">
         <v>500</v>
@@ -8383,10 +8364,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C208" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8415,7 +8396,7 @@
         <v>18</v>
       </c>
       <c r="C209" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8444,7 +8425,7 @@
         <v>18</v>
       </c>
       <c r="C210" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8470,10 +8451,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C211" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8499,7 +8480,7 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C212" t="s">
         <v>42</v>
@@ -8528,7 +8509,7 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C213" t="s">
         <v>42</v>
@@ -8560,7 +8541,7 @@
         <v>62</v>
       </c>
       <c r="C214" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8589,7 +8570,7 @@
         <v>62</v>
       </c>
       <c r="C215" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8615,10 +8596,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C216" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8647,7 +8628,7 @@
         <v>65</v>
       </c>
       <c r="C217" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -8676,7 +8657,7 @@
         <v>65</v>
       </c>
       <c r="C218" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D218">
         <v>500</v>
@@ -8705,7 +8686,7 @@
         <v>65</v>
       </c>
       <c r="C219" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8731,10 +8712,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C220" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8763,7 +8744,7 @@
         <v>66</v>
       </c>
       <c r="C221" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8792,7 +8773,7 @@
         <v>66</v>
       </c>
       <c r="C222" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8821,7 +8802,7 @@
         <v>66</v>
       </c>
       <c r="C223" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8847,10 +8828,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C224" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8879,7 +8860,7 @@
         <v>67</v>
       </c>
       <c r="C225" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8905,10 +8886,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
+        <v>68</v>
+      </c>
+      <c r="C226" t="s">
         <v>67</v>
-      </c>
-      <c r="C226" t="s">
-        <v>69</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8937,7 +8918,7 @@
         <v>68</v>
       </c>
       <c r="C227" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8966,7 +8947,7 @@
         <v>68</v>
       </c>
       <c r="C228" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -8995,7 +8976,7 @@
         <v>68</v>
       </c>
       <c r="C229" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -9024,7 +9005,7 @@
         <v>68</v>
       </c>
       <c r="C230" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -9050,10 +9031,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
+        <v>20</v>
+      </c>
+      <c r="C231" t="s">
         <v>68</v>
-      </c>
-      <c r="C231" t="s">
-        <v>36</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -9079,10 +9060,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C232" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -9111,7 +9092,7 @@
         <v>51</v>
       </c>
       <c r="C233" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -9140,7 +9121,7 @@
         <v>51</v>
       </c>
       <c r="C234" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -9169,7 +9150,7 @@
         <v>51</v>
       </c>
       <c r="C235" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -9195,10 +9176,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C236" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -9227,7 +9208,7 @@
         <v>26</v>
       </c>
       <c r="C237" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -9253,10 +9234,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
+        <v>72</v>
+      </c>
+      <c r="C238" t="s">
         <v>26</v>
-      </c>
-      <c r="C238" t="s">
-        <v>53</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9285,7 +9266,7 @@
         <v>72</v>
       </c>
       <c r="C239" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9311,10 +9292,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C240" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9343,7 +9324,7 @@
         <v>34</v>
       </c>
       <c r="C241" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9369,10 +9350,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
+        <v>32</v>
+      </c>
+      <c r="C242" t="s">
         <v>34</v>
-      </c>
-      <c r="C242" t="s">
-        <v>32</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9398,10 +9379,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C243" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9430,7 +9411,7 @@
         <v>58</v>
       </c>
       <c r="C244" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9459,7 +9440,7 @@
         <v>58</v>
       </c>
       <c r="C245" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9488,7 +9469,7 @@
         <v>58</v>
       </c>
       <c r="C246" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9514,7 +9495,7 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C247" t="s">
         <v>51</v>
@@ -9543,10 +9524,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C248" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9575,7 +9556,7 @@
         <v>53</v>
       </c>
       <c r="C249" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9604,7 +9585,7 @@
         <v>53</v>
       </c>
       <c r="C250" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9630,10 +9611,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C251" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D251">
         <v>500</v>
@@ -9659,10 +9640,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C252" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D252">
         <v>500</v>
@@ -9691,7 +9672,7 @@
         <v>36</v>
       </c>
       <c r="C253" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9717,10 +9698,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C254" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9746,10 +9727,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="C255" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9775,7 +9756,7 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C256" t="s">
         <v>22</v>
@@ -9804,10 +9785,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C257" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9836,7 +9817,7 @@
         <v>75</v>
       </c>
       <c r="C258" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9862,10 +9843,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C259" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9891,10 +9872,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C260" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9920,10 +9901,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C261" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9952,7 +9933,7 @@
         <v>58</v>
       </c>
       <c r="C262" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9981,7 +9962,7 @@
         <v>58</v>
       </c>
       <c r="C263" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -10007,7 +9988,7 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C264" t="s">
         <v>66</v>
@@ -10036,10 +10017,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
+        <v>68</v>
+      </c>
+      <c r="C265" t="s">
         <v>67</v>
-      </c>
-      <c r="C265" t="s">
-        <v>66</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -10065,10 +10046,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
+        <v>36</v>
+      </c>
+      <c r="C266" t="s">
         <v>68</v>
-      </c>
-      <c r="C266" t="s">
-        <v>67</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -10094,10 +10075,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C267" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -10123,10 +10104,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="C268" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -10152,10 +10133,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C269" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -10181,10 +10162,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C270" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -10210,10 +10191,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C271" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -10242,7 +10223,7 @@
         <v>48</v>
       </c>
       <c r="C272" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -10271,7 +10252,7 @@
         <v>48</v>
       </c>
       <c r="C273" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10300,7 +10281,7 @@
         <v>48</v>
       </c>
       <c r="C274" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D274">
         <v>500</v>
@@ -10326,10 +10307,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C275" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D275">
         <v>500</v>
@@ -10355,10 +10336,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C276" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D276">
         <v>500</v>
@@ -10384,10 +10365,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C277" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D277">
         <v>500</v>
@@ -10413,10 +10394,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C278" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D278">
         <v>500</v>
@@ -10442,10 +10423,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C279" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D279">
         <v>500</v>
@@ -10471,10 +10452,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C280" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D280">
         <v>500</v>
@@ -10500,10 +10481,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C281" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D281">
         <v>500</v>
@@ -10529,10 +10510,10 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C282" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D282">
         <v>500</v>
@@ -10558,19 +10539,19 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C283" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D283">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E283">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F283">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G283">
         <v>10000000</v>
@@ -10587,19 +10568,19 @@
         <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="C284" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D284">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E284">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F284">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G284">
         <v>10000000</v>
@@ -10616,10 +10597,10 @@
         <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C285" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D285">
         <v>10000</v>
@@ -10645,10 +10626,10 @@
         <v>12</v>
       </c>
       <c r="B286" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C286" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="D286">
         <v>10000</v>
@@ -10674,10 +10655,10 @@
         <v>12</v>
       </c>
       <c r="B287" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C287" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D287">
         <v>10000</v>
@@ -10703,10 +10684,10 @@
         <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C288" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D288">
         <v>10000</v>
@@ -10732,10 +10713,10 @@
         <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C289" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D289">
         <v>10000</v>
@@ -10761,10 +10742,10 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C290" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D290">
         <v>10000</v>
@@ -10790,10 +10771,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C291" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D291">
         <v>10000</v>
@@ -10819,10 +10800,10 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C292" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D292">
         <v>10000</v>
@@ -10848,10 +10829,10 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C293" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D293">
         <v>10000</v>
@@ -10877,10 +10858,10 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C294" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D294">
         <v>10000</v>
@@ -10906,10 +10887,10 @@
         <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C295" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D295">
         <v>10000</v>
@@ -10935,10 +10916,10 @@
         <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C296" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D296">
         <v>10000</v>
@@ -10964,10 +10945,10 @@
         <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C297" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D297">
         <v>10000</v>
@@ -10993,10 +10974,10 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C298" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -11022,19 +11003,19 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C299" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D299">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E299">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F299">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G299">
         <v>10000000</v>
@@ -11051,19 +11032,19 @@
         <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C300" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D300">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E300">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F300">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G300">
         <v>10000000</v>
@@ -11072,64 +11053,6 @@
         <v>1000</v>
       </c>
       <c r="I300">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A301" t="s">
-        <v>12</v>
-      </c>
-      <c r="B301" t="s">
-        <v>53</v>
-      </c>
-      <c r="C301" t="s">
-        <v>75</v>
-      </c>
-      <c r="D301">
-        <v>500</v>
-      </c>
-      <c r="E301">
-        <v>500</v>
-      </c>
-      <c r="F301">
-        <v>1</v>
-      </c>
-      <c r="G301">
-        <v>10000000</v>
-      </c>
-      <c r="H301">
-        <v>1000</v>
-      </c>
-      <c r="I301">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A302" t="s">
-        <v>12</v>
-      </c>
-      <c r="B302" t="s">
-        <v>75</v>
-      </c>
-      <c r="C302" t="s">
-        <v>30</v>
-      </c>
-      <c r="D302">
-        <v>500</v>
-      </c>
-      <c r="E302">
-        <v>500</v>
-      </c>
-      <c r="F302">
-        <v>1</v>
-      </c>
-      <c r="G302">
-        <v>10000000</v>
-      </c>
-      <c r="H302">
-        <v>1000</v>
-      </c>
-      <c r="I302">
         <v>1</v>
       </c>
     </row>
@@ -11292,7 +11215,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -11303,7 +11226,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>0.55586415</v>
@@ -11314,7 +11237,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16">
         <v>796.255</v>
@@ -11325,7 +11248,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17">
         <v>7.5617455199999997</v>
@@ -11336,7 +11259,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>5.7643000000000007E-2</v>
@@ -11347,7 +11270,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19">
         <v>0.53100926999999998</v>
@@ -11358,7 +11281,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C20">
         <v>8.6795214499999993</v>
@@ -11369,7 +11292,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21">
         <v>1.9156527500000002</v>
@@ -11380,7 +11303,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22">
         <v>0.16949973000000002</v>
@@ -11391,7 +11314,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23">
         <v>6.3309600000000021E-2</v>
@@ -11402,7 +11325,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>16.46245</v>
@@ -11413,7 +11336,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C25">
         <v>19.829690269999997</v>
@@ -11424,7 +11347,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26">
         <v>3.9959299999999995</v>
@@ -11435,7 +11358,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>0.6516687699999999</v>
@@ -11446,7 +11369,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28">
         <v>5.2113180000000002E-2</v>
@@ -11457,7 +11380,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29">
         <v>4.2744726999999996</v>
@@ -11468,7 +11391,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30">
         <v>0.44941999999999999</v>
@@ -11922,7 +11845,7 @@
         <v>36</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>-453.32799999999997</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -11941,7 +11864,7 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -11996,7 +11919,7 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78">
         <v>-10.747</v>
@@ -12150,7 +12073,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -12612,7 +12535,7 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -12667,7 +12590,7 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12711,7 +12634,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12722,7 +12645,7 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12733,7 +12656,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12744,7 +12667,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12755,7 +12678,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12766,7 +12689,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12777,7 +12700,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12788,7 +12711,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12799,7 +12722,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12810,7 +12733,7 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -12821,7 +12744,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12832,7 +12755,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12843,7 +12766,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12854,7 +12777,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12865,7 +12788,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12876,7 +12799,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12887,7 +12810,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12898,7 +12821,7 @@
         <v>11</v>
       </c>
       <c r="B160" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -12909,7 +12832,7 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C161">
         <v>0</v>

--- a/01_data/01_input_data/02_processed/data_base_case_russia.xlsx
+++ b/01_data/01_input_data/02_processed/data_base_case_russia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3785F8-1B7B-45C1-A856-923DC1D3743A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBEFDCC-44C9-42D8-95A5-4D569E27EEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="97">
   <si>
     <t>Commodities</t>
   </si>
@@ -372,8 +372,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1143,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B150"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2036,314 +2037,234 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B113" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B114" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B115" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B116" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B117" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B119" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="B120" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
+        <v>82</v>
+      </c>
+      <c r="B121" t="s">
         <v>77</v>
-      </c>
-      <c r="B121" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B122" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B123" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B129" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B130" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B131" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B133" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B135" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B136" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B137" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B140" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>91</v>
-      </c>
-      <c r="B141" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>92</v>
-      </c>
-      <c r="B142" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>93</v>
-      </c>
-      <c r="B143" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>94</v>
-      </c>
-      <c r="B144" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>95</v>
-      </c>
-      <c r="B145" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>96</v>
-      </c>
-      <c r="B146" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>82</v>
-      </c>
-      <c r="B147" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>82</v>
-      </c>
-      <c r="B148" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>40</v>
-      </c>
-      <c r="B149" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>53</v>
-      </c>
-      <c r="B150" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2353,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I300"/>
+  <dimension ref="A1:I281"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -3614,10 +3535,10 @@
         <v>59</v>
       </c>
       <c r="D44">
-        <v>141.21850000000001</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="E44">
-        <v>141.21850000000001</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -5035,10 +4956,10 @@
         <v>67</v>
       </c>
       <c r="D93">
-        <v>145.31745000000001</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="E93">
-        <v>145.31745000000001</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -5528,10 +5449,10 @@
         <v>65</v>
       </c>
       <c r="D110">
-        <v>831.32399999999996</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="E110">
-        <v>831.32399999999996</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -5557,10 +5478,10 @@
         <v>66</v>
       </c>
       <c r="D111">
-        <v>188.19399999999999</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="E111">
-        <v>188.19399999999999</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -5731,10 +5652,10 @@
         <v>22</v>
       </c>
       <c r="D117">
-        <v>177.79150000000001</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E117">
-        <v>177.79150000000001</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -5760,10 +5681,10 @@
         <v>68</v>
       </c>
       <c r="D118">
-        <v>210.25094999999999</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="E118">
-        <v>210.25094999999999</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -5818,10 +5739,10 @@
         <v>34</v>
       </c>
       <c r="D120">
-        <v>267.07049999999998</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="E120">
-        <v>267.07049999999998</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -5841,16 +5762,16 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C121" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D121">
-        <v>173.667</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E121">
-        <v>173.667</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5870,10 +5791,10 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" t="s">
         <v>75</v>
-      </c>
-      <c r="C122" t="s">
-        <v>30</v>
       </c>
       <c r="D122">
         <v>439.27749999999992</v>
@@ -5899,16 +5820,16 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C123" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D123">
-        <v>439.27749999999992</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="E123">
-        <v>439.27749999999992</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5928,16 +5849,16 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C124" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D124">
-        <v>118.77099999999999</v>
+        <v>486.91</v>
       </c>
       <c r="E124">
-        <v>118.77099999999999</v>
+        <v>486.91</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5957,16 +5878,16 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C125" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D125">
-        <v>486.91</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E125">
-        <v>486.91</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -5986,16 +5907,16 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C126" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D126">
-        <v>144.17500000000001</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="E126">
-        <v>144.17500000000001</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -6015,16 +5936,16 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D127">
-        <v>49.494</v>
+        <v>12.1837</v>
       </c>
       <c r="E127">
-        <v>49.494</v>
+        <v>12.1837</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -6044,16 +5965,16 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C128" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D128">
-        <v>816.06700000000012</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="E128">
-        <v>816.06700000000012</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -6072,17 +5993,17 @@
       <c r="A129" t="s">
         <v>11</v>
       </c>
-      <c r="B129" t="s">
-        <v>58</v>
+      <c r="B129" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C129" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D129">
-        <v>188.88749999999999</v>
+        <v>421.21</v>
       </c>
       <c r="E129">
-        <v>188.88749999999999</v>
+        <v>421.21</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -6102,16 +6023,16 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C130" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D130">
-        <v>89.716999999999999</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E130">
-        <v>89.716999999999999</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6131,16 +6052,16 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C131" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D131">
-        <v>170.63749999999999</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="E131">
-        <v>170.63749999999999</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6160,16 +6081,16 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C132" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="D132">
-        <v>12.1837</v>
+        <v>351.714</v>
       </c>
       <c r="E132">
-        <v>12.1837</v>
+        <v>351.714</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6189,16 +6110,16 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C133" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D133">
-        <v>256.15699999999998</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="E133">
-        <v>256.15699999999998</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -6218,16 +6139,16 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C134" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D134">
-        <v>180.20050000000001</v>
+        <v>207.5025</v>
       </c>
       <c r="E134">
-        <v>180.20050000000001</v>
+        <v>207.5025</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -6247,16 +6168,16 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C135" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D135">
-        <v>421.21</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="E135">
-        <v>421.21</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -6276,16 +6197,16 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C136" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D136">
-        <v>123.04150000000001</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="E136">
-        <v>123.04150000000001</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6305,16 +6226,16 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C137" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D137">
-        <v>161.62200000000001</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E137">
-        <v>161.62200000000001</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6334,16 +6255,16 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C138" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D138">
-        <v>455.15499999999997</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E138">
-        <v>455.15499999999997</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6363,16 +6284,16 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C139" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="D139">
-        <v>351.714</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E139">
-        <v>351.714</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6392,16 +6313,16 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C140" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D140">
-        <v>167.75399999999999</v>
+        <v>421.21</v>
       </c>
       <c r="E140">
-        <v>167.75399999999999</v>
+        <v>421.21</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -6421,16 +6342,16 @@
         <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D141">
-        <v>207.5025</v>
+        <v>14.965</v>
       </c>
       <c r="E141">
-        <v>207.5025</v>
+        <v>14.965</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -6447,19 +6368,19 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C142" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D142">
-        <v>513.19000000000005</v>
+        <v>10000</v>
       </c>
       <c r="E142">
-        <v>513.19000000000005</v>
+        <v>10000</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -6468,7 +6389,7 @@
         <v>10000000</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -6476,19 +6397,19 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D143">
-        <v>82.927999999999997</v>
+        <v>10000</v>
       </c>
       <c r="E143">
-        <v>82.927999999999997</v>
+        <v>10000</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -6497,7 +6418,7 @@
         <v>10000000</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -6505,19 +6426,19 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C144" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D144">
-        <v>67.451999999999998</v>
+        <v>10000</v>
       </c>
       <c r="E144">
-        <v>67.451999999999998</v>
+        <v>10000</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -6526,7 +6447,7 @@
         <v>10000000</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -6534,19 +6455,19 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C145" t="s">
         <v>22</v>
       </c>
       <c r="D145">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="E145">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6555,7 +6476,7 @@
         <v>10000000</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -6563,19 +6484,19 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C146" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D146">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="E146">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -6584,7 +6505,7 @@
         <v>10000000</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -6592,19 +6513,19 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D147">
-        <v>144.17500000000001</v>
+        <v>10000</v>
       </c>
       <c r="E147">
-        <v>144.17500000000001</v>
+        <v>10000</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -6613,7 +6534,7 @@
         <v>10000000</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -6621,19 +6542,19 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C148" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D148">
-        <v>123.04150000000001</v>
+        <v>10000</v>
       </c>
       <c r="E148">
-        <v>123.04150000000001</v>
+        <v>10000</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -6642,7 +6563,7 @@
         <v>10000000</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -6650,19 +6571,19 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C149" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D149">
-        <v>421.21</v>
+        <v>10000</v>
       </c>
       <c r="E149">
-        <v>421.21</v>
+        <v>10000</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -6671,7 +6592,7 @@
         <v>10000000</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -6679,19 +6600,19 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C150" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D150">
-        <v>14.965</v>
+        <v>10000</v>
       </c>
       <c r="E150">
-        <v>14.965</v>
+        <v>10000</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -6700,7 +6621,7 @@
         <v>10000000</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -6711,16 +6632,16 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C151" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D151">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E151">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -6740,16 +6661,16 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C152" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D152">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E152">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -6769,16 +6690,16 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C153" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D153">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E153">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -6798,16 +6719,16 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="C154" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="D154">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E154">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -6827,16 +6748,16 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C155" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D155">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E155">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -6856,16 +6777,16 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C156" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D156">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E156">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -6885,16 +6806,16 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C157" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D157">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E157">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -6914,16 +6835,16 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C158" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D158">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E158">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -6943,16 +6864,16 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C159" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D159">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E159">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -6972,16 +6893,16 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C160" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D160">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E160">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -7001,16 +6922,16 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C161" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D161">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E161">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -7030,16 +6951,16 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C162" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D162">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E162">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -7059,16 +6980,16 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C163" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D163">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E163">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -7088,16 +7009,16 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C164" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D164">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E164">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -7117,16 +7038,16 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C165" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D165">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E165">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -7146,16 +7067,16 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C166" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D166">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E166">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -7175,16 +7096,16 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C167" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D167">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E167">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -7204,16 +7125,16 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D168">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E168">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -7233,16 +7154,16 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C169" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D169">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E169">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -7262,16 +7183,16 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C170" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D170">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E170">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -7291,16 +7212,16 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C171" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D171">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E171">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -7320,16 +7241,16 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D172">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E172">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -7349,16 +7270,16 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C173" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D173">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E173">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -7378,16 +7299,16 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C174" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D174">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E174">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -7407,16 +7328,16 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C175" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D175">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E175">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -7436,16 +7357,16 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C176" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D176">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E176">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -7465,16 +7386,16 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C177" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D177">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E177">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -7494,16 +7415,16 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C178" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D178">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E178">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -7523,16 +7444,16 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C179" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D179">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E179">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -7552,16 +7473,16 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C180" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D180">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E180">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -7581,16 +7502,16 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C181" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D181">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E181">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -7610,16 +7531,16 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C182" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D182">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E182">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -7639,16 +7560,16 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C183" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D183">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E183">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -7668,16 +7589,16 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
+        <v>60</v>
+      </c>
+      <c r="C184" t="s">
         <v>42</v>
       </c>
-      <c r="C184" t="s">
-        <v>16</v>
-      </c>
       <c r="D184">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E184">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -7697,16 +7618,16 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C185" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D185">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E185">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -7726,16 +7647,16 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C186" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D186">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E186">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -7755,16 +7676,16 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C187" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D187">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E187">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -7784,16 +7705,16 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C188" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D188">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E188">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -7813,16 +7734,16 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C189" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D189">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E189">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -7842,16 +7763,16 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C190" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D190">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E190">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -7871,16 +7792,16 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C191" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D191">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E191">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -7900,16 +7821,16 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
+        <v>61</v>
+      </c>
+      <c r="C192" t="s">
         <v>42</v>
       </c>
-      <c r="C192" t="s">
-        <v>63</v>
-      </c>
       <c r="D192">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E192">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -7929,16 +7850,16 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C193" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D193">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E193">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -7958,16 +7879,16 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C194" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D194">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E194">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F194">
         <v>1</v>
@@ -7987,16 +7908,16 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C195" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D195">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E195">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -8016,16 +7937,16 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C196" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D196">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E196">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -8045,16 +7966,16 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C197" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D197">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E197">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F197">
         <v>1</v>
@@ -8074,16 +7995,16 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C198" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D198">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E198">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F198">
         <v>1</v>
@@ -8103,16 +8024,16 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C199" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D199">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E199">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -8132,16 +8053,16 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C200" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D200">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E200">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F200">
         <v>1</v>
@@ -8161,16 +8082,16 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C201" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D201">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E201">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -8190,16 +8111,16 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C202" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D202">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E202">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -8219,16 +8140,16 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="C203" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D203">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E203">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -8248,16 +8169,16 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C204" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D204">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E204">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F204">
         <v>1</v>
@@ -8277,16 +8198,16 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C205" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D205">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E205">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -8306,16 +8227,16 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C206" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D206">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E206">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F206">
         <v>1</v>
@@ -8335,16 +8256,16 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C207" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D207">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E207">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F207">
         <v>1</v>
@@ -8364,16 +8285,16 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C208" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D208">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E208">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F208">
         <v>1</v>
@@ -8393,16 +8314,16 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C209" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D209">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E209">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -8422,16 +8343,16 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C210" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D210">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E210">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F210">
         <v>1</v>
@@ -8451,16 +8372,16 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C211" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D211">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E211">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F211">
         <v>1</v>
@@ -8480,16 +8401,16 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C212" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D212">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E212">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -8509,16 +8430,16 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C213" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D213">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E213">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -8538,16 +8459,16 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C214" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D214">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E214">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -8567,16 +8488,16 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C215" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D215">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E215">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F215">
         <v>1</v>
@@ -8596,16 +8517,16 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C216" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D216">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E216">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -8625,16 +8546,16 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C217" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D217">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E217">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -8654,16 +8575,16 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C218" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D218">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E218">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F218">
         <v>1</v>
@@ -8683,16 +8604,16 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C219" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D219">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E219">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F219">
         <v>1</v>
@@ -8712,16 +8633,16 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C220" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D220">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E220">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F220">
         <v>1</v>
@@ -8741,16 +8662,16 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C221" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D221">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E221">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F221">
         <v>1</v>
@@ -8770,16 +8691,16 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="C222" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D222">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E222">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F222">
         <v>1</v>
@@ -8799,16 +8720,16 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
+        <v>51</v>
+      </c>
+      <c r="C223" t="s">
         <v>66</v>
       </c>
-      <c r="C223" t="s">
-        <v>51</v>
-      </c>
       <c r="D223">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E223">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F223">
         <v>1</v>
@@ -8828,16 +8749,16 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C224" t="s">
         <v>68</v>
       </c>
       <c r="D224">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E224">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F224">
         <v>1</v>
@@ -8857,16 +8778,16 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C225" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D225">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E225">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F225">
         <v>1</v>
@@ -8886,16 +8807,16 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C226" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D226">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E226">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F226">
         <v>1</v>
@@ -8915,16 +8836,16 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C227" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D227">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E227">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F227">
         <v>1</v>
@@ -8944,16 +8865,16 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C228" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D228">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E228">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F228">
         <v>1</v>
@@ -8973,16 +8894,16 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C229" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D229">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E229">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F229">
         <v>1</v>
@@ -9002,16 +8923,16 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C230" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D230">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E230">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F230">
         <v>1</v>
@@ -9031,16 +8952,16 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C231" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D231">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E231">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F231">
         <v>1</v>
@@ -9060,16 +8981,16 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C232" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D232">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E232">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F232">
         <v>1</v>
@@ -9089,16 +9010,16 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C233" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D233">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E233">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F233">
         <v>1</v>
@@ -9118,16 +9039,16 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C234" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D234">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E234">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F234">
         <v>1</v>
@@ -9147,16 +9068,16 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C235" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D235">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E235">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F235">
         <v>1</v>
@@ -9176,16 +9097,16 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C236" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D236">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E236">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F236">
         <v>1</v>
@@ -9205,16 +9126,16 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C237" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D237">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E237">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F237">
         <v>1</v>
@@ -9234,16 +9155,16 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C238" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D238">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E238">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F238">
         <v>1</v>
@@ -9263,16 +9184,16 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C239" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D239">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E239">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F239">
         <v>1</v>
@@ -9292,16 +9213,16 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C240" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D240">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E240">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F240">
         <v>1</v>
@@ -9321,16 +9242,16 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C241" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="D241">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E241">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F241">
         <v>1</v>
@@ -9350,16 +9271,16 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="C242" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D242">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E242">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F242">
         <v>1</v>
@@ -9379,16 +9300,16 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C243" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D243">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E243">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F243">
         <v>1</v>
@@ -9408,16 +9329,16 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C244" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="D244">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E244">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F244">
         <v>1</v>
@@ -9437,16 +9358,16 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C245" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D245">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E245">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F245">
         <v>1</v>
@@ -9466,16 +9387,16 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C246" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D246">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E246">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F246">
         <v>1</v>
@@ -9495,16 +9416,16 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C247" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D247">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E247">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -9524,16 +9445,16 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C248" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D248">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E248">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F248">
         <v>1</v>
@@ -9553,16 +9474,16 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C249" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="D249">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E249">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F249">
         <v>1</v>
@@ -9585,13 +9506,13 @@
         <v>53</v>
       </c>
       <c r="C250" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D250">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E250">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F250">
         <v>1</v>
@@ -9611,16 +9532,16 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C251" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D251">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E251">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F251">
         <v>1</v>
@@ -9640,16 +9561,16 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C252" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D252">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E252">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -9669,16 +9590,16 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="C253" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D253">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E253">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F253">
         <v>1</v>
@@ -9698,16 +9619,16 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C254" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D254">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E254">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F254">
         <v>1</v>
@@ -9727,16 +9648,16 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C255" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D255">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E255">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F255">
         <v>1</v>
@@ -9756,16 +9677,16 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C256" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D256">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E256">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F256">
         <v>1</v>
@@ -9785,16 +9706,16 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C257" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D257">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E257">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F257">
         <v>1</v>
@@ -9814,16 +9735,16 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C258" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D258">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E258">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F258">
         <v>1</v>
@@ -9843,16 +9764,16 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C259" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D259">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E259">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -9872,16 +9793,16 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C260" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D260">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E260">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F260">
         <v>1</v>
@@ -9901,16 +9822,16 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C261" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D261">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E261">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F261">
         <v>1</v>
@@ -9930,16 +9851,16 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C262" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D262">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E262">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F262">
         <v>1</v>
@@ -9959,16 +9880,16 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C263" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D263">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E263">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -9988,19 +9909,19 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C264" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D264">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E264">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F264">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G264">
         <v>10000000</v>
@@ -10017,19 +9938,19 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C265" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D265">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E265">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F265">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G265">
         <v>10000000</v>
@@ -10046,19 +9967,19 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C266" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D266">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E266">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F266">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G266">
         <v>10000000</v>
@@ -10075,19 +9996,19 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C267" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D267">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E267">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F267">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G267">
         <v>10000000</v>
@@ -10104,19 +10025,19 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C268" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D268">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E268">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F268">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G268">
         <v>10000000</v>
@@ -10133,19 +10054,19 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C269" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D269">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E269">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F269">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G269">
         <v>10000000</v>
@@ -10162,19 +10083,19 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="C270" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D270">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E270">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F270">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G270">
         <v>10000000</v>
@@ -10191,19 +10112,19 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="C271" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D271">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E271">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F271">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G271">
         <v>10000000</v>
@@ -10220,19 +10141,19 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C272" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D272">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E272">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F272">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G272">
         <v>10000000</v>
@@ -10249,19 +10170,19 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D273">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E273">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F273">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G273">
         <v>10000000</v>
@@ -10278,19 +10199,19 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C274" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D274">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E274">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F274">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G274">
         <v>10000000</v>
@@ -10307,19 +10228,19 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="C275" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D275">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E275">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F275">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G275">
         <v>10000000</v>
@@ -10336,19 +10257,19 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="C276" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="D276">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E276">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F276">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G276">
         <v>10000000</v>
@@ -10365,19 +10286,19 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C277" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D277">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E277">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F277">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G277">
         <v>10000000</v>
@@ -10394,19 +10315,19 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="C278" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="D278">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E278">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F278">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G278">
         <v>10000000</v>
@@ -10423,19 +10344,19 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="C279" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D279">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E279">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F279">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G279">
         <v>10000000</v>
@@ -10452,16 +10373,16 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C280" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D280">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E280">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -10481,16 +10402,16 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C281" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D281">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E281">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F281">
         <v>1</v>
@@ -10502,557 +10423,6 @@
         <v>1000</v>
       </c>
       <c r="I281">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A282" t="s">
-        <v>12</v>
-      </c>
-      <c r="B282" t="s">
-        <v>40</v>
-      </c>
-      <c r="C282" t="s">
-        <v>79</v>
-      </c>
-      <c r="D282">
-        <v>500</v>
-      </c>
-      <c r="E282">
-        <v>500</v>
-      </c>
-      <c r="F282">
-        <v>1</v>
-      </c>
-      <c r="G282">
-        <v>10000000</v>
-      </c>
-      <c r="H282">
-        <v>1000</v>
-      </c>
-      <c r="I282">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
-        <v>12</v>
-      </c>
-      <c r="B283" t="s">
-        <v>80</v>
-      </c>
-      <c r="C283" t="s">
-        <v>74</v>
-      </c>
-      <c r="D283">
-        <v>10000</v>
-      </c>
-      <c r="E283">
-        <v>10000</v>
-      </c>
-      <c r="F283">
-        <v>100</v>
-      </c>
-      <c r="G283">
-        <v>10000000</v>
-      </c>
-      <c r="H283">
-        <v>1000</v>
-      </c>
-      <c r="I283">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A284" t="s">
-        <v>12</v>
-      </c>
-      <c r="B284" t="s">
-        <v>81</v>
-      </c>
-      <c r="C284" t="s">
-        <v>82</v>
-      </c>
-      <c r="D284">
-        <v>10000</v>
-      </c>
-      <c r="E284">
-        <v>10000</v>
-      </c>
-      <c r="F284">
-        <v>100</v>
-      </c>
-      <c r="G284">
-        <v>10000000</v>
-      </c>
-      <c r="H284">
-        <v>1000</v>
-      </c>
-      <c r="I284">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A285" t="s">
-        <v>12</v>
-      </c>
-      <c r="B285" t="s">
-        <v>83</v>
-      </c>
-      <c r="C285" t="s">
-        <v>60</v>
-      </c>
-      <c r="D285">
-        <v>10000</v>
-      </c>
-      <c r="E285">
-        <v>10000</v>
-      </c>
-      <c r="F285">
-        <v>100</v>
-      </c>
-      <c r="G285">
-        <v>10000000</v>
-      </c>
-      <c r="H285">
-        <v>1000</v>
-      </c>
-      <c r="I285">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
-        <v>12</v>
-      </c>
-      <c r="B286" t="s">
-        <v>84</v>
-      </c>
-      <c r="C286" t="s">
-        <v>16</v>
-      </c>
-      <c r="D286">
-        <v>10000</v>
-      </c>
-      <c r="E286">
-        <v>10000</v>
-      </c>
-      <c r="F286">
-        <v>100</v>
-      </c>
-      <c r="G286">
-        <v>10000000</v>
-      </c>
-      <c r="H286">
-        <v>1000</v>
-      </c>
-      <c r="I286">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A287" t="s">
-        <v>12</v>
-      </c>
-      <c r="B287" t="s">
-        <v>85</v>
-      </c>
-      <c r="C287" t="s">
-        <v>68</v>
-      </c>
-      <c r="D287">
-        <v>10000</v>
-      </c>
-      <c r="E287">
-        <v>10000</v>
-      </c>
-      <c r="F287">
-        <v>100</v>
-      </c>
-      <c r="G287">
-        <v>10000000</v>
-      </c>
-      <c r="H287">
-        <v>1000</v>
-      </c>
-      <c r="I287">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A288" t="s">
-        <v>12</v>
-      </c>
-      <c r="B288" t="s">
-        <v>86</v>
-      </c>
-      <c r="C288" t="s">
-        <v>24</v>
-      </c>
-      <c r="D288">
-        <v>10000</v>
-      </c>
-      <c r="E288">
-        <v>10000</v>
-      </c>
-      <c r="F288">
-        <v>100</v>
-      </c>
-      <c r="G288">
-        <v>10000000</v>
-      </c>
-      <c r="H288">
-        <v>1000</v>
-      </c>
-      <c r="I288">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A289" t="s">
-        <v>12</v>
-      </c>
-      <c r="B289" t="s">
-        <v>87</v>
-      </c>
-      <c r="C289" t="s">
-        <v>62</v>
-      </c>
-      <c r="D289">
-        <v>10000</v>
-      </c>
-      <c r="E289">
-        <v>10000</v>
-      </c>
-      <c r="F289">
-        <v>100</v>
-      </c>
-      <c r="G289">
-        <v>10000000</v>
-      </c>
-      <c r="H289">
-        <v>1000</v>
-      </c>
-      <c r="I289">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
-        <v>12</v>
-      </c>
-      <c r="B290" t="s">
-        <v>88</v>
-      </c>
-      <c r="C290" t="s">
-        <v>18</v>
-      </c>
-      <c r="D290">
-        <v>10000</v>
-      </c>
-      <c r="E290">
-        <v>10000</v>
-      </c>
-      <c r="F290">
-        <v>100</v>
-      </c>
-      <c r="G290">
-        <v>10000000</v>
-      </c>
-      <c r="H290">
-        <v>1000</v>
-      </c>
-      <c r="I290">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A291" t="s">
-        <v>12</v>
-      </c>
-      <c r="B291" t="s">
-        <v>89</v>
-      </c>
-      <c r="C291" t="s">
-        <v>20</v>
-      </c>
-      <c r="D291">
-        <v>10000</v>
-      </c>
-      <c r="E291">
-        <v>10000</v>
-      </c>
-      <c r="F291">
-        <v>100</v>
-      </c>
-      <c r="G291">
-        <v>10000000</v>
-      </c>
-      <c r="H291">
-        <v>1000</v>
-      </c>
-      <c r="I291">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A292" t="s">
-        <v>12</v>
-      </c>
-      <c r="B292" t="s">
-        <v>90</v>
-      </c>
-      <c r="C292" t="s">
-        <v>66</v>
-      </c>
-      <c r="D292">
-        <v>10000</v>
-      </c>
-      <c r="E292">
-        <v>10000</v>
-      </c>
-      <c r="F292">
-        <v>100</v>
-      </c>
-      <c r="G292">
-        <v>10000000</v>
-      </c>
-      <c r="H292">
-        <v>1000</v>
-      </c>
-      <c r="I292">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A293" t="s">
-        <v>12</v>
-      </c>
-      <c r="B293" t="s">
-        <v>91</v>
-      </c>
-      <c r="C293" t="s">
-        <v>59</v>
-      </c>
-      <c r="D293">
-        <v>10000</v>
-      </c>
-      <c r="E293">
-        <v>10000</v>
-      </c>
-      <c r="F293">
-        <v>100</v>
-      </c>
-      <c r="G293">
-        <v>10000000</v>
-      </c>
-      <c r="H293">
-        <v>1000</v>
-      </c>
-      <c r="I293">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A294" t="s">
-        <v>12</v>
-      </c>
-      <c r="B294" t="s">
-        <v>92</v>
-      </c>
-      <c r="C294" t="s">
-        <v>67</v>
-      </c>
-      <c r="D294">
-        <v>10000</v>
-      </c>
-      <c r="E294">
-        <v>10000</v>
-      </c>
-      <c r="F294">
-        <v>100</v>
-      </c>
-      <c r="G294">
-        <v>10000000</v>
-      </c>
-      <c r="H294">
-        <v>1000</v>
-      </c>
-      <c r="I294">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A295" t="s">
-        <v>12</v>
-      </c>
-      <c r="B295" t="s">
-        <v>93</v>
-      </c>
-      <c r="C295" t="s">
-        <v>65</v>
-      </c>
-      <c r="D295">
-        <v>10000</v>
-      </c>
-      <c r="E295">
-        <v>10000</v>
-      </c>
-      <c r="F295">
-        <v>100</v>
-      </c>
-      <c r="G295">
-        <v>10000000</v>
-      </c>
-      <c r="H295">
-        <v>1000</v>
-      </c>
-      <c r="I295">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A296" t="s">
-        <v>12</v>
-      </c>
-      <c r="B296" t="s">
-        <v>94</v>
-      </c>
-      <c r="C296" t="s">
-        <v>64</v>
-      </c>
-      <c r="D296">
-        <v>10000</v>
-      </c>
-      <c r="E296">
-        <v>10000</v>
-      </c>
-      <c r="F296">
-        <v>100</v>
-      </c>
-      <c r="G296">
-        <v>10000000</v>
-      </c>
-      <c r="H296">
-        <v>1000</v>
-      </c>
-      <c r="I296">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A297" t="s">
-        <v>12</v>
-      </c>
-      <c r="B297" t="s">
-        <v>95</v>
-      </c>
-      <c r="C297" t="s">
-        <v>36</v>
-      </c>
-      <c r="D297">
-        <v>10000</v>
-      </c>
-      <c r="E297">
-        <v>10000</v>
-      </c>
-      <c r="F297">
-        <v>100</v>
-      </c>
-      <c r="G297">
-        <v>10000000</v>
-      </c>
-      <c r="H297">
-        <v>1000</v>
-      </c>
-      <c r="I297">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A298" t="s">
-        <v>12</v>
-      </c>
-      <c r="B298" t="s">
-        <v>96</v>
-      </c>
-      <c r="C298" t="s">
-        <v>34</v>
-      </c>
-      <c r="D298">
-        <v>10000</v>
-      </c>
-      <c r="E298">
-        <v>10000</v>
-      </c>
-      <c r="F298">
-        <v>100</v>
-      </c>
-      <c r="G298">
-        <v>10000000</v>
-      </c>
-      <c r="H298">
-        <v>1000</v>
-      </c>
-      <c r="I298">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A299" t="s">
-        <v>12</v>
-      </c>
-      <c r="B299" t="s">
-        <v>53</v>
-      </c>
-      <c r="C299" t="s">
-        <v>75</v>
-      </c>
-      <c r="D299">
-        <v>500</v>
-      </c>
-      <c r="E299">
-        <v>500</v>
-      </c>
-      <c r="F299">
-        <v>1</v>
-      </c>
-      <c r="G299">
-        <v>10000000</v>
-      </c>
-      <c r="H299">
-        <v>1000</v>
-      </c>
-      <c r="I299">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A300" t="s">
-        <v>12</v>
-      </c>
-      <c r="B300" t="s">
-        <v>75</v>
-      </c>
-      <c r="C300" t="s">
-        <v>30</v>
-      </c>
-      <c r="D300">
-        <v>500</v>
-      </c>
-      <c r="E300">
-        <v>500</v>
-      </c>
-      <c r="F300">
-        <v>1</v>
-      </c>
-      <c r="G300">
-        <v>10000000</v>
-      </c>
-      <c r="H300">
-        <v>1000</v>
-      </c>
-      <c r="I300">
         <v>1</v>
       </c>
     </row>
@@ -11938,24 +11308,24 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>-24.864095362311311</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>-10.40036286731274</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
@@ -11963,7 +11333,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -11974,7 +11344,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -11985,7 +11355,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -11996,7 +11366,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -12007,7 +11377,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -12018,7 +11388,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -12029,7 +11399,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -12040,7 +11410,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -12051,7 +11421,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -12062,7 +11432,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -12073,7 +11443,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -12084,7 +11454,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -12095,7 +11465,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -12106,7 +11476,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -12117,7 +11487,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -12128,7 +11498,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -12139,7 +11509,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -12150,7 +11520,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -12161,7 +11531,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -12172,7 +11542,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -12183,7 +11553,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -12194,7 +11564,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -12205,7 +11575,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -12216,7 +11586,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -12227,7 +11597,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -12238,7 +11608,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -12249,7 +11619,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -12260,7 +11630,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -12271,7 +11641,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -12282,7 +11652,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -12293,7 +11663,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -12304,7 +11674,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -12315,7 +11685,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -12326,7 +11696,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -12337,7 +11707,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -12348,7 +11718,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -12359,7 +11729,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -12370,7 +11740,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -12381,7 +11751,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -12392,7 +11762,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -12403,7 +11773,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -12414,7 +11784,7 @@
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -12425,7 +11795,7 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -12436,7 +11806,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -12447,7 +11817,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -12458,7 +11828,7 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -12469,7 +11839,7 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -12480,7 +11850,7 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -12491,7 +11861,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -12502,7 +11872,7 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -12513,7 +11883,7 @@
         <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -12524,7 +11894,7 @@
         <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -12535,7 +11905,7 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -12546,7 +11916,7 @@
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -12557,7 +11927,7 @@
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12568,7 +11938,7 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -12579,7 +11949,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12590,7 +11960,7 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12598,13 +11968,13 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C140">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -12612,7 +11982,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12620,13 +11990,13 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -12634,7 +12004,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12645,7 +12015,7 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12656,7 +12026,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12667,7 +12037,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12678,7 +12048,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12689,7 +12059,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12700,7 +12070,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12711,7 +12081,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12722,7 +12092,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12733,7 +12103,7 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -12744,7 +12114,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12755,7 +12125,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12766,7 +12136,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12777,7 +12147,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12788,7 +12158,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12799,7 +12169,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12810,7 +12180,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12818,10 +12188,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -12832,7 +12202,7 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -12843,7 +12213,7 @@
         <v>11</v>
       </c>
       <c r="B162" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -12854,7 +12224,7 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -12862,10 +12232,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B164" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -12876,7 +12246,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -12884,13 +12254,13 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C166">
-        <v>-24.864095362311311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -12898,7 +12268,7 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -12906,13 +12276,13 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
         <v>70</v>
       </c>
       <c r="C168">
-        <v>-10.40036286731274</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
